--- a/Tables/aov_shoot_all_table_GlucoseQuantity.xlsx
+++ b/Tables/aov_shoot_all_table_GlucoseQuantity.xlsx
@@ -399,12 +399,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.974</t>
+          <t>1.977</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.162</t>
         </is>
       </c>
     </row>
@@ -443,17 +443,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0.050</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.204</t>
+          <t>3.348</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>0.070</t>
         </is>
       </c>
     </row>
@@ -470,7 +470,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.678</t>
+          <t>1.676</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -492,17 +492,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>0.024</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.508</t>
+          <t>2.294</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0.133</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.188</t>
+          <t>1.190</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
